--- a/currentbuild/ValueSet-lmdi-medicationadministrationstatus.xlsx
+++ b/currentbuild/ValueSet-lmdi-medicationadministrationstatus.xlsx
@@ -120,7 +120,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-admin-status</t>
+    <t>http://terminology.hl7.org/CodeSystem/medication-admin-status</t>
   </si>
 </sst>
 </file>

--- a/currentbuild/ValueSet-lmdi-medicationadministrationstatus.xlsx
+++ b/currentbuild/ValueSet-lmdi-medicationadministrationstatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.8</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/ValueSet-lmdi-medicationadministrationstatus.xlsx
+++ b/currentbuild/ValueSet-lmdi-medicationadministrationstatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/ValueSet-lmdi-medicationadministrationstatus.xlsx
+++ b/currentbuild/ValueSet-lmdi-medicationadministrationstatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.1.3</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/ValueSet-lmdi-medicationadministrationstatus.xlsx
+++ b/currentbuild/ValueSet-lmdi-medicationadministrationstatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.3</t>
+    <t>1.1.4</t>
   </si>
   <si>
     <t>Name</t>
